--- a/artfynd/A 48779-2023 artfynd.xlsx
+++ b/artfynd/A 48779-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128358431</v>
+        <v>128358423</v>
       </c>
       <c r="B2" t="n">
-        <v>92677</v>
+        <v>92644</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1968</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546504</v>
+        <v>546493</v>
       </c>
       <c r="R2" t="n">
-        <v>6961450</v>
+        <v>6961507</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128358423</v>
+        <v>128358431</v>
       </c>
       <c r="B3" t="n">
-        <v>92639</v>
+        <v>92682</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>1968</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546493</v>
+        <v>546504</v>
       </c>
       <c r="R3" t="n">
-        <v>6961507</v>
+        <v>6961450</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -872,7 +872,7 @@
         <v>128358382</v>
       </c>
       <c r="B4" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128358399</v>
       </c>
       <c r="B5" t="n">
-        <v>92637</v>
+        <v>92642</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128358391</v>
       </c>
       <c r="B6" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128358412</v>
       </c>
       <c r="B7" t="n">
-        <v>91305</v>
+        <v>91310</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128362249</v>
       </c>
       <c r="B8" t="n">
-        <v>92673</v>
+        <v>92678</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 48779-2023 artfynd.xlsx
+++ b/artfynd/A 48779-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128358423</v>
+        <v>128358431</v>
       </c>
       <c r="B2" t="n">
-        <v>92644</v>
+        <v>92774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>1968</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546493</v>
+        <v>546504</v>
       </c>
       <c r="R2" t="n">
-        <v>6961507</v>
+        <v>6961450</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128358431</v>
+        <v>128358423</v>
       </c>
       <c r="B3" t="n">
-        <v>92682</v>
+        <v>92736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1968</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546504</v>
+        <v>546493</v>
       </c>
       <c r="R3" t="n">
-        <v>6961450</v>
+        <v>6961507</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -872,7 +872,7 @@
         <v>128358382</v>
       </c>
       <c r="B4" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128358399</v>
       </c>
       <c r="B5" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128358391</v>
       </c>
       <c r="B6" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128358412</v>
       </c>
       <c r="B7" t="n">
-        <v>91310</v>
+        <v>91402</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128362249</v>
       </c>
       <c r="B8" t="n">
-        <v>92678</v>
+        <v>92770</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 48779-2023 artfynd.xlsx
+++ b/artfynd/A 48779-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128358431</v>
+        <v>128358423</v>
       </c>
       <c r="B2" t="n">
-        <v>92774</v>
+        <v>92736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1968</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546504</v>
+        <v>546493</v>
       </c>
       <c r="R2" t="n">
-        <v>6961450</v>
+        <v>6961507</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128358423</v>
+        <v>128358431</v>
       </c>
       <c r="B3" t="n">
-        <v>92736</v>
+        <v>92774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>1968</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546493</v>
+        <v>546504</v>
       </c>
       <c r="R3" t="n">
-        <v>6961507</v>
+        <v>6961450</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>

--- a/artfynd/A 48779-2023 artfynd.xlsx
+++ b/artfynd/A 48779-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128358423</v>
+        <v>128358431</v>
       </c>
       <c r="B2" t="n">
-        <v>92736</v>
+        <v>92786</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>1968</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546493</v>
+        <v>546504</v>
       </c>
       <c r="R2" t="n">
-        <v>6961507</v>
+        <v>6961450</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128358431</v>
+        <v>128358423</v>
       </c>
       <c r="B3" t="n">
-        <v>92774</v>
+        <v>92748</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1968</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546504</v>
+        <v>546493</v>
       </c>
       <c r="R3" t="n">
-        <v>6961450</v>
+        <v>6961507</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -872,7 +872,7 @@
         <v>128358382</v>
       </c>
       <c r="B4" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128358399</v>
       </c>
       <c r="B5" t="n">
-        <v>92734</v>
+        <v>92746</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128358391</v>
       </c>
       <c r="B6" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128358412</v>
       </c>
       <c r="B7" t="n">
-        <v>91402</v>
+        <v>91414</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128362249</v>
       </c>
       <c r="B8" t="n">
-        <v>92770</v>
+        <v>92782</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 48779-2023 artfynd.xlsx
+++ b/artfynd/A 48779-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128358431</v>
+        <v>128358423</v>
       </c>
       <c r="B2" t="n">
-        <v>92786</v>
+        <v>92750</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1968</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546504</v>
+        <v>546493</v>
       </c>
       <c r="R2" t="n">
-        <v>6961450</v>
+        <v>6961507</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128358423</v>
+        <v>128358431</v>
       </c>
       <c r="B3" t="n">
-        <v>92748</v>
+        <v>92788</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>1968</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546493</v>
+        <v>546504</v>
       </c>
       <c r="R3" t="n">
-        <v>6961507</v>
+        <v>6961450</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -872,7 +872,7 @@
         <v>128358382</v>
       </c>
       <c r="B4" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128358399</v>
       </c>
       <c r="B5" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128358391</v>
       </c>
       <c r="B6" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128358412</v>
       </c>
       <c r="B7" t="n">
-        <v>91414</v>
+        <v>91416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128362249</v>
       </c>
       <c r="B8" t="n">
-        <v>92782</v>
+        <v>92784</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 48779-2023 artfynd.xlsx
+++ b/artfynd/A 48779-2023 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>128358382</v>
       </c>
       <c r="B4" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128358391</v>
       </c>
       <c r="B6" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 48779-2023 artfynd.xlsx
+++ b/artfynd/A 48779-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128358423</v>
+        <v>128358431</v>
       </c>
       <c r="B2" t="n">
-        <v>92750</v>
+        <v>92789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>1968</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546493</v>
+        <v>546504</v>
       </c>
       <c r="R2" t="n">
-        <v>6961507</v>
+        <v>6961450</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128358431</v>
+        <v>128358423</v>
       </c>
       <c r="B3" t="n">
-        <v>92788</v>
+        <v>92751</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1968</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546504</v>
+        <v>546493</v>
       </c>
       <c r="R3" t="n">
-        <v>6961450</v>
+        <v>6961507</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -872,7 +872,7 @@
         <v>128358382</v>
       </c>
       <c r="B4" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128358399</v>
       </c>
       <c r="B5" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128358391</v>
       </c>
       <c r="B6" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128358412</v>
       </c>
       <c r="B7" t="n">
-        <v>91416</v>
+        <v>91417</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128362249</v>
       </c>
       <c r="B8" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 48779-2023 artfynd.xlsx
+++ b/artfynd/A 48779-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128358431</v>
       </c>
       <c r="B2" t="n">
-        <v>92789</v>
+        <v>92816</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128358423</v>
       </c>
       <c r="B3" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128358382</v>
       </c>
       <c r="B4" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128358399</v>
       </c>
       <c r="B5" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128358391</v>
       </c>
       <c r="B6" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128358412</v>
       </c>
       <c r="B7" t="n">
-        <v>91417</v>
+        <v>91444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128362249</v>
       </c>
       <c r="B8" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 48779-2023 artfynd.xlsx
+++ b/artfynd/A 48779-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128358431</v>
+        <v>128358423</v>
       </c>
       <c r="B2" t="n">
-        <v>92816</v>
+        <v>92788</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1968</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546504</v>
+        <v>546493</v>
       </c>
       <c r="R2" t="n">
-        <v>6961450</v>
+        <v>6961507</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128358423</v>
+        <v>128358431</v>
       </c>
       <c r="B3" t="n">
-        <v>92778</v>
+        <v>92828</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>1968</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546493</v>
+        <v>546504</v>
       </c>
       <c r="R3" t="n">
-        <v>6961507</v>
+        <v>6961450</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -872,7 +872,7 @@
         <v>128358382</v>
       </c>
       <c r="B4" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128358399</v>
       </c>
       <c r="B5" t="n">
-        <v>92776</v>
+        <v>92786</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128358391</v>
       </c>
       <c r="B6" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128358412</v>
       </c>
       <c r="B7" t="n">
-        <v>91444</v>
+        <v>91454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128362249</v>
       </c>
       <c r="B8" t="n">
-        <v>92812</v>
+        <v>92823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1270,21 +1270,12 @@
       <c r="E8" t="n">
         <v>5449</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>

--- a/artfynd/A 48779-2023 artfynd.xlsx
+++ b/artfynd/A 48779-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128358423</v>
+        <v>128358431</v>
       </c>
       <c r="B2" t="n">
-        <v>92788</v>
+        <v>92828</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>1968</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546493</v>
+        <v>546504</v>
       </c>
       <c r="R2" t="n">
-        <v>6961507</v>
+        <v>6961450</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128358431</v>
+        <v>128358423</v>
       </c>
       <c r="B3" t="n">
-        <v>92828</v>
+        <v>92788</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1968</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546504</v>
+        <v>546493</v>
       </c>
       <c r="R3" t="n">
-        <v>6961450</v>
+        <v>6961507</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>

--- a/artfynd/A 48779-2023 artfynd.xlsx
+++ b/artfynd/A 48779-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128358431</v>
+        <v>128358423</v>
       </c>
       <c r="B2" t="n">
-        <v>92828</v>
+        <v>92788</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1968</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546504</v>
+        <v>546493</v>
       </c>
       <c r="R2" t="n">
-        <v>6961450</v>
+        <v>6961507</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128358423</v>
+        <v>128358431</v>
       </c>
       <c r="B3" t="n">
-        <v>92788</v>
+        <v>92828</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>1968</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546493</v>
+        <v>546504</v>
       </c>
       <c r="R3" t="n">
-        <v>6961507</v>
+        <v>6961450</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>

--- a/artfynd/A 48779-2023 artfynd.xlsx
+++ b/artfynd/A 48779-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128358423</v>
       </c>
       <c r="B2" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128358431</v>
       </c>
       <c r="B3" t="n">
-        <v>92828</v>
+        <v>92832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128358382</v>
       </c>
       <c r="B4" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128358399</v>
       </c>
       <c r="B5" t="n">
-        <v>92786</v>
+        <v>92790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128358391</v>
       </c>
       <c r="B6" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128358412</v>
       </c>
       <c r="B7" t="n">
-        <v>91454</v>
+        <v>91458</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128362249</v>
       </c>
       <c r="B8" t="n">
-        <v>92823</v>
+        <v>92827</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 48779-2023 artfynd.xlsx
+++ b/artfynd/A 48779-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128358423</v>
+        <v>128358412</v>
       </c>
       <c r="B2" t="n">
-        <v>92792</v>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546493</v>
+        <v>546536</v>
       </c>
       <c r="R2" t="n">
-        <v>6961507</v>
+        <v>6961462</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -775,7 +775,7 @@
         <v>128358431</v>
       </c>
       <c r="B3" t="n">
-        <v>92832</v>
+        <v>93231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128358382</v>
+        <v>128358399</v>
       </c>
       <c r="B4" t="n">
-        <v>98636</v>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546598</v>
+        <v>546582</v>
       </c>
       <c r="R4" t="n">
-        <v>6961493</v>
+        <v>6961501</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128358399</v>
+        <v>128358423</v>
       </c>
       <c r="B5" t="n">
-        <v>92790</v>
+        <v>93191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546582</v>
+        <v>546493</v>
       </c>
       <c r="R5" t="n">
-        <v>6961501</v>
+        <v>6961507</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128358391</v>
+        <v>128358382</v>
       </c>
       <c r="B6" t="n">
-        <v>98636</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546572</v>
+        <v>546598</v>
       </c>
       <c r="R6" t="n">
-        <v>6961514</v>
+        <v>6961493</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128358412</v>
+        <v>128358391</v>
       </c>
       <c r="B7" t="n">
-        <v>91458</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546536</v>
+        <v>546572</v>
       </c>
       <c r="R7" t="n">
-        <v>6961462</v>
+        <v>6961514</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1254,94 +1254,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>128362249</v>
-      </c>
-      <c r="B8" t="n">
-        <v>92827</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>5449</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Båthusviken, Båthusviken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>546521</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6961512</v>
-      </c>
-      <c r="S8" t="n">
-        <v>25</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Hällesjö</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Vincent Heldt Cassel</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Vincent Heldt Cassel</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48779-2023 artfynd.xlsx
+++ b/artfynd/A 48779-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128358412</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128358431</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128358399</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128358423</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128358382</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,8 +1284,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128358391</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>